--- a/Colaboradores_2.4/Colaboradores/Base_historica_Grupo_Empresarial.xlsx
+++ b/Colaboradores_2.4/Colaboradores/Base_historica_Grupo_Empresarial.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\954108\Desktop\codigos_py\Presentaciones\IPN_Colaboradores\Colaboradores\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3894E399-F024-489F-8D95-E6BD6E853933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Periodo</t>
   </si>
@@ -43,14 +49,74 @@
     <t>OFICINA DE LA PRESIDENCIA</t>
   </si>
   <si>
-    <t>2Q´26</t>
+    <t>1Q´21</t>
+  </si>
+  <si>
+    <t>2Q´21</t>
+  </si>
+  <si>
+    <t>3Q´21</t>
+  </si>
+  <si>
+    <t>4Q´21</t>
+  </si>
+  <si>
+    <t>1Q´22</t>
+  </si>
+  <si>
+    <t>2Q´22</t>
+  </si>
+  <si>
+    <t>3Q´22</t>
+  </si>
+  <si>
+    <t>4Q´22</t>
+  </si>
+  <si>
+    <t>1Q´23</t>
+  </si>
+  <si>
+    <t>2Q´23</t>
+  </si>
+  <si>
+    <t>3Q´23</t>
+  </si>
+  <si>
+    <t>4Q´23</t>
+  </si>
+  <si>
+    <t>1Q´24</t>
+  </si>
+  <si>
+    <t>2Q´24</t>
+  </si>
+  <si>
+    <t>3Q´24</t>
+  </si>
+  <si>
+    <t>4Q´24</t>
+  </si>
+  <si>
+    <t>1Q´25</t>
+  </si>
+  <si>
+    <t>2Q´25</t>
+  </si>
+  <si>
+    <t>3Q´25</t>
+  </si>
+  <si>
+    <t>4Q´25</t>
+  </si>
+  <si>
+    <t>1Q´26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,13 +153,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -131,7 +205,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -165,6 +239,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -199,9 +274,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -374,11 +450,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -407,32 +483,441 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>0.7158478971885427</v>
+        <v>0.625</v>
       </c>
       <c r="C2">
-        <v>0.6883924784391346</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="D2">
-        <v>0.5945267958950968</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="E2">
-        <v>0.6480573368540173</v>
-      </c>
-      <c r="F2">
-        <v>0.5039370078740157</v>
-      </c>
-      <c r="G2">
-        <v>0.671875</v>
-      </c>
-      <c r="H2">
-        <v>0.7628968253968254</v>
-      </c>
-      <c r="I2">
+        <v>0.435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="C3">
+        <v>0.45</v>
+      </c>
+      <c r="D3">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="E3">
+        <v>0.33100000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="C4">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="D4">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="E4">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>0.67</v>
+      </c>
+      <c r="C5">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="D5">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="E5">
+        <v>0.36199999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="C6">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="D6">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="E6">
+        <v>0.495</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="C7">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="D7">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="E7">
+        <v>0.376</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="C8">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="D8">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="E8">
+        <v>0.49399999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="C9">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="D9">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="E9">
+        <v>0.51300000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="C10">
+        <v>0.627</v>
+      </c>
+      <c r="D10">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="E10">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>0.74099999999999999</v>
+      </c>
+      <c r="C11">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="D11">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="E11">
+        <v>0.60199999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="C12">
+        <v>0.67600000000000005</v>
+      </c>
+      <c r="D12">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.61899999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>0.745</v>
+      </c>
+      <c r="C13">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="D13">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="E13">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="C14">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="D14">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="E14">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="C15">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="D15">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="E15">
+        <v>0.623</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="C16">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="D16">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="E16">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="F16">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="H16">
+        <v>0.72399999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="C17">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="D17">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="E17">
+        <v>0.62</v>
+      </c>
+      <c r="F17">
+        <v>0.53</v>
+      </c>
+      <c r="G17">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="H17">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="I17">
+        <v>0.85699999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="C18">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="D18">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="E18">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="F18">
+        <v>0.443</v>
+      </c>
+      <c r="G18">
+        <v>0.67600000000000005</v>
+      </c>
+      <c r="H18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="I18">
+        <v>0.81200000000000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="C19">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="D19">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="E19">
+        <v>0.62</v>
+      </c>
+      <c r="F19">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="G19">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="H19">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="C20">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="D20">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E20">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="F20">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="G20">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="H20">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="I20">
+        <v>0.64300000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="C21">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="D21">
+        <v>0.61</v>
+      </c>
+      <c r="E21">
+        <v>0.627</v>
+      </c>
+      <c r="F21">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="G21">
+        <v>0.65</v>
+      </c>
+      <c r="H21">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="I21">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="C22">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="D22">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="E22">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="F22">
+        <v>0.504</v>
+      </c>
+      <c r="G22">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="H22">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="I22">
         <v>1</v>
       </c>
     </row>
